--- a/用例步骤.xlsx
+++ b/用例步骤.xlsx
@@ -10,10 +10,10 @@
     <sheet name="目录" sheetId="1" r:id="rId1"/>
     <sheet name="testcase" sheetId="2" r:id="rId2"/>
     <sheet name="拓扑图" sheetId="3" r:id="rId3"/>
-    <sheet name="测试结果" sheetId="4" r:id="rId4"/>
+    <sheet name="页面元素" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">testcase!$A$1:$K$162</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">testcase!$A$1:$K$172</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="90">
   <si>
     <t>ID</t>
   </si>
@@ -233,6 +233,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>功能用例</t>
     </r>
     <r>
@@ -313,6 +319,81 @@
 6&gt;电脑自动获取地址后可用访问外网</t>
   </si>
   <si>
+    <t>功能用例/端口冲突检测</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 验证研发提供端口冲突静态端口列表的完整性与准确性</t>
+  </si>
+  <si>
+    <t>设备出厂状态</t>
+  </si>
+  <si>
+    <t>1，登录路由器，并且跳转到#network/firewall/portmapping
+2，点击添加按钮//*[@id="mapping_operate"]在//*[@id="yruo_firewall_port_mappingmiquo355_src"]里面填写192.168.1.100/24在//*[@id="yruo_firewall_port_mappingmiquo355_to_dst"]填写10.10.10.10在//*[@id="yruo_firewall_port_mappingmiquo355_to_dport"]里面填写111
+3，在//*[@id="yruo_firewall_port_mappingmiquo355_dport"] 填写测试port 然后点击保存//*[@id="save"]
+，点击保存后需要做的是，如果有弹窗则先点击弹窗的ok按钮关闭弹窗 然后去判断填写的测试port是否在22,53,1701,9001,68,500,4500,123,1,58,7574,9993,520里面的值，如果在测通过 如果不在直接整个用例失败；点击保存后如果没有弹窗，则直接判断填写的测试port是否在22,53,1701,9001,68,500,4500,123,1,58,7574,9993,520里面的值，如果在则整个用例失败，如果不在这个里面也没有弹窗则测试通过
+4，重复步骤3，需要遍历1到65535所有的端口，其中有一个失败则整个用例都是失败的，其中任何一个端口失败都视为整个用例失败</t>
+  </si>
+  <si>
+    <t>设备防火墙界面检查静态端口冲突</t>
+  </si>
+  <si>
+    <t>1，跳转到防火墙页面，在http后面的输入框，遍历所有研发提供的端口，填写一个端口点击一次保存，必须弹端口冲突提示，不弹则测试失败 依次类推 这个页面的 https telnet ssh ftp 均按照这个逻辑实现</t>
+  </si>
+  <si>
+    <t>设备去串口1界面端口冲突</t>
+  </si>
+  <si>
+    <t>参照D:\WK\Milesight\AUTO\port_check.py里面的def configure_Serial1_ports(driver, wait, ports):所不同的是这次输入的端口号不一样需要和用例“端口冲突检测测试（全端口扫描）”里面保持一直 另外就是这些端口都必须弹窗提醒端口冲突，如果不弹在证明用例失败</t>
+  </si>
+  <si>
+    <t>设备去串口2界面端口冲突</t>
+  </si>
+  <si>
+    <t>参照D:\WK\Milesight\AUTO\port_check.py里面的def configure_Serial2_ports(driver, wait, ports):所不同的是这次输入的端口号不一样需要和用例“端口冲突检测测试（全端口扫描）”里面保持一直 另外就是这些端口都必须弹窗提醒端口冲突，如果不弹在证明用例失败</t>
+  </si>
+  <si>
+    <t>设备去modbus TCP界面端口冲突</t>
+  </si>
+  <si>
+    <t>参照D:\WK\Milesight\AUTO\port_check.py里面的def configure_Modbus_RTU_Over_TCP_ports(driver, wait, ports, vpn_config):所不同的是这次输入的端口号不一样需要和用例“端口冲突检测测试（全端口扫描）”里面保持一直 另外就是这些端口都必须弹窗提醒端口冲突，如果不弹在证明用例失败</t>
+  </si>
+  <si>
+    <t>设备去SNMP界面端口冲突</t>
+  </si>
+  <si>
+    <t>参照D:\WK\Milesight\AUTO\port_check.py里面的def configure_snmp_ports(driver, wait, ports, email_config):所不同的是这次输入的端口号不一样需要和用例“端口冲突检测测试（全端口扫描）”里面保持一直 另外就是这些端口都必须弹窗提醒端口冲突，如果不弹在证明用例失败</t>
+  </si>
+  <si>
+    <t>设备去GPS界面端口冲突</t>
+  </si>
+  <si>
+    <t>1,登录路由器，并且跳转到#industrial/gps/gps页面
+2，点击启用gps按钮//*[@id="1_enable"]然后点击保存//*[@id="save"]
+3，跳转到#industrial/gps/ipforwarding页面
+4，点击启用//*[@id="1_enable"]然后在//*[@id="1_type"]的下拉框里面选择value="server"
+5，参照上面的实现逻辑在本地端口//*[@id="1_local_port"]填入端口并检测是否弹窗</t>
+  </si>
+  <si>
+    <t>设备open vpn界面端口冲突</t>
+  </si>
+  <si>
+    <t>参照D:\WK\Milesight\AUTO\port_check.py里面的def configure_vpn_server_ports(driver, wait, ports, vpn_config):所不同的是这次输入的端口号不一样需要和用例“端口冲突检测测试（全端口扫描）”里面保持一直 另外就是这些端口都必须弹窗提醒端口冲突，如果不弹在证明用例失败</t>
+  </si>
+  <si>
+    <t>自定义端口两两冲突检测</t>
+  </si>
+  <si>
+    <t>1，去防火墙界面配置ftp端口为1111（配置方法参照用例：设备防火墙界面检查静态端口冲突）这里要区别是只配置ftp端口配置完后要先启用ftp勾选然后保存并点击应用
+2，去openvpn界面配置端口为1111（配置方法参照用例：设备open vpn界面端口冲突）这里需要弹窗提醒才算通过
+3，去端口映射界面配置端口为1111（配置方法参照用例：端口冲突检测测试（全端口扫描）里面配置端口映射部分）这里需要弹窗提醒才算通过
+4，去设备串口1界面端口配置端口为1111（配置方法参照用例：设备去串口1界面端口冲突）这里需要弹窗提醒才算通过
+5，去设备串口2界面端口配置端口为1111（配置方法参照用例：设备去串口2界面端口冲突）这里需要弹窗提醒才算通过
+6，去设备modbus TCP界面端口配置端口为1111（配置方法参照用例：设备去modbus TCP界面端口冲突）这里需要弹窗提醒才算通过
+7，去SNMP 页面配置端口为1111（配置方法参照用例：设备去SNMP界面端口冲突）这里需要弹窗提醒才算通过
+8，去GPS 页面配置端口为1111（配置方法参照用例：设备去GPS界面端口冲突）这里需要弹窗提醒才算通过</t>
+  </si>
+  <si>
     <t>功能用例/服务/MQTT</t>
   </si>
   <si>
@@ -358,6 +439,239 @@
     <t>顺利执行过程不报错</t>
   </si>
   <si>
+    <t xml:space="preserve"> mqtt配置页面"请求主题"上报功能-驻网上</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1&gt;登录路由器，跳转到#industrial/mqtt/status页面
+2&gt;找到&lt;button class="button btn-add" id="4_add_btn" type="button" style="width: 10%;"&gt;&lt;/button&gt;并点击添加
+3&gt;点击//*[@id="1_enabled"]启用按钮
+4&gt;填写//*[@id="1_mqtt_name"]里面的内容为test
+5&gt;填写//*[@id="1_m_server_addr"]里面的地址为自动化weib MQTT服务器地址
+6&gt;勾选//*[@id="1_enable_user_credentials"]
+7&gt;填写//*[@id="1_username"]用户信息admim
+8&gt;填写//*[@id="1_password"]密码password
+9&gt;填写//*[@id="1_req_topic"]为mqtt/system/request
+10&gt;填写//*[@id="1_resp_topic"]为mqtt/system/response
+11&gt;点击保存//*[@id="1_save"]
+12&gt;点击应用按钮
+13&gt;等带3s后刷新页面检测//*[@id="mqtt_list"]/div[2]/div[1]/div[4]/span是否为已连接，如果一直检测不到就等待页面配置的300s超时后提示，MQTT服务器连接失败，结束测试，一直刷新检测直到已连接成功
+14&gt;到首页检查蜂窝状态为“当前链路”（和之前蜂窝状态检查一致）
+15&gt;PC自己模拟一个MQTT客户端去连接同一个服务器，这个MQTT客户端订阅和发布的主题与路由器上面的保持一直，然后客户端去mqtt/system/request发送内容为：{"id":"1","status":"cellular"}
+查看路由器回复信息{
+  "code": "2",
+  "id": "1",
+  "time": "2025-11-26T11:10:41Z",
+  "status": "cellular",
+  "data": {
+    "modem": {
+      "modem_status": "Ready",
+      "model": "EC20F",
+      "version": "EC20CEHCLGR08A02M1G",
+      "cur_sim": "SIM1",
+      "signal": "31asu (-51dBm)",
+      "band": "4G(B1)",
+      "rsrp": "-77dbm",
+      "rsrq": "-6db",
+      "sinr": "26db",
+      "register": "Registered (Home network)",
+      "imsi": "460115211257157",
+      "iccid": "89860324245920231421",
+      "net_provider": "CHN-CT",
+      "net_type": "FDD LTE",
+      "plmnid": "46011",
+      "lac": "5f0c",
+      "cellid": "e0b70b",
+      "imei": "869128065899956"
+    },
+    "network": {
+      "vpn1": {
+        "status": "Connected",
+        "ip": "10.3.218.11",
+        "netmask": "255.255.255.248",
+        "gate": "10.3.218.12",
+        "dns": "218.85.152.99",
+        "sec_dns": "218.85.157.99",
+        "dnsv6": "::",
+        "sec_dnsv6": "::",
+        "ipv6": "fe80::409:48ff:fe62:c962/64",
+        "gatev6": "::",
+        "time": "0 days, 00:13:50"
+      },
+      "vpn2": {
+        "status": "Disconnected",
+        "ip": "0.0.0.0",
+        "netmask": "0.0.0.0",
+        "gate": "0.0.0.0",
+        "dns": "0.0.0.0",
+        "sec_dns": "0.0.0.0",
+        "dnsv6": "::",
+        "sec_dnsv6": "::",
+        "ipv6": "::",
+        "gatev6": "::",
+        "time": "0 days, 00:00:00"
+      },
+      "vpn3": {
+        "status": "Disconnected",
+        "ip": "0.0.0.0",
+        "netmask": "0.0.0.0",
+        "gate": "0.0.0.0",
+        "dns": "0.0.0.0",
+        "sec_dns": "0.0.0.0",
+        "dnsv6": "::",
+        "sec_dnsv6": "::",
+        "ipv6": "::",
+        "gatev6": "::",
+        "time": "0 days, 00:00:00"
+      }
+    },
+    "statistics": {
+      "sim1": "RX: 0.0 MiB   TX: 0.0 MiB   ALL: 0.0 MiB",
+      "sim2": "RX: 0.0 MiB   TX: 0.0 MiB   ALL: 0.0 MiB"
+    }
+  }
+}并且格式一致，内容中除了time不用一致其他都要一致其中顺序可以不一致,这里的data的内容要与页面#status/cellular里面的内容一致，每一项都要比对是否一致，任何一项不一致都说明用例失败，要打印出不一致的点
+</t>
+  </si>
+  <si>
+    <t>mqtt配置页面"请求主题"上报功能-未驻网上</t>
+  </si>
+  <si>
+    <t>1. 登录路由器，去设置蜂窝支持的网络制式为2G（制造蜂窝未注册成功场景）
+2.跳转到 #industrial/mqtt/status 页面
+3. 找到添加按钮并点击
+4. 启用MQTT客户端
+5. 填写MQTT配置信息（名称、服务器地址、用户名、密码）
+6. 配置request主题为 mqtt/system/request
+7. 配置response主题为 mqtt/system/response
+8. 保存配置并应用
+9. 等待MQTT连接建立（最长300秒）
+10. 获取页面当前蜂窝状态作为基准
+11. PC端模拟MQTT客户端，发送cellular状态查询命令: {"id":"1","status":"cellular"}
+12. 接收并解析路由器响应的JSON数据{
+  "code": "2",
+  "id": "1",
+  "time": "2025-11-26T11:10:41Z",
+  "status": "cellular",
+  "data": {
+    "modem": {
+      "modem_status": "Ready",
+      "model": "EC20F",
+      "version": "EC20CEHCLGR08A02M1G",
+      "cur_sim": "SIM1",
+      "signal": "31asu (-51dBm)",
+      "band": "4G(B1)",
+      "rsrp": "-77dbm",
+      "rsrq": "-6db",
+      "sinr": "26db",
+      "register": "Registered (Home network)",
+      "imsi": "460115211257157",
+      "iccid": "89860324245920231421",
+      "net_provider": "CHN-CT",
+      "net_type": "FDD LTE",
+      "plmnid": "46011",
+      "lac": "5f0c",
+      "cellid": "e0b70b",
+      "imei": "869128065899956"
+    },
+    "network": {
+      "vpn1": {
+        "status": "Connected",
+        "ip": "10.3.218.11",
+        "netmask": "255.255.255.248",
+        "gate": "10.3.218.12",
+        "dns": "218.85.152.99",
+        "sec_dns": "218.85.157.99",
+        "dnsv6": "::",
+        "sec_dnsv6": "::",
+        "ipv6": "fe80::409:48ff:fe62:c962/64",
+        "gatev6": "::",
+        "time": "0 days, 00:13:50"
+      },
+      "vpn2": {
+        "status": "Disconnected",
+        "ip": "0.0.0.0",
+        "netmask": "0.0.0.0",
+        "gate": "0.0.0.0",
+        "dns": "0.0.0.0",
+        "sec_dns": "0.0.0.0",
+        "dnsv6": "::",
+        "sec_dnsv6": "::",
+        "ipv6": "::",
+        "gatev6": "::",
+        "time": "0 days, 00:00:00"
+      },
+      "vpn3": {
+        "status": "Disconnected",
+        "ip": "0.0.0.0",
+        "netmask": "0.0.0.0",
+        "gate": "0.0.0.0",
+        "dns": "0.0.0.0",
+        "sec_dns": "0.0.0.0",
+        "dnsv6": "::",
+        "sec_dnsv6": "::",
+        "ipv6": "::",
+        "gatev6": "::",
+        "time": "0 days, 00:00:00"
+      }
+    },
+    "statistics": {
+      "sim1": "RX: 0.0 MiB   TX: 0.0 MiB   ALL: 0.0 MiB",
+      "sim2": "RX: 0.0 MiB   TX: 0.0 MiB   ALL: 0.0 MiB"
+    }
+  }
+}
+13. 验证响应数据格式正确
+14. 将响应data字段与页面 #status/cellular 数据逐一对比
+15. 验证所有字段一致（除time字段外，顺序可不一致）</t>
+  </si>
+  <si>
+    <t>MQTT连接成功
+路由器返回正确格式的cellular状态数据
+响应数据与页面显示完全一致
+任何字段不一致都视为测试失败</t>
+  </si>
+  <si>
+    <t>稳定性</t>
+  </si>
+  <si>
+    <t>多设备反复升级稳定性测试</t>
+  </si>
+  <si>
+    <t>1，我有两台，固定ip 192.168.50.17  用户admin 密码admin1   固定ip：192.168.50.18 用户admin 密码admin1 需要对这两台设备进行循环升级新旧版本，新版本路径：E:\GIT\ROUTER_TEST\docs\upload\new 旧版本路径：E:\GIT\ROUTER_TEST\docs\upload\old
+2，升级旧版本的过程：跳转到#maintenance/upgrade/upgrade页面，在//*[@id="1_file_url"]里面上传E:\GIT\ROUTER_TEST\docs\upload\old下面的版本然后点击升级按钮//*[@id="1_file_import"]
+4，等待能在页面设置的300s超时时间内重新登录成功路由则证明升级成功一次
+5，然后跳转到#maintenance/upgrade/upgrade页面，在//*[@id="1_file_url"]里面上传E:\GIT\ROUTER_TEST\docs\upload\new下面的版本然后点击升级按钮//*[@id="1_file_import"]
+6，等待能在页面设置的300s超时时间内重新登录成功路由则证明升级成功一次
+7,重复上面的循环升级1000次
+8，两台设备独立进行并行测试</t>
+  </si>
+  <si>
+    <t>（特别说明50.17这个设备对应的串口是com8  50.18这个设备对应的是com7）登录串口然后输入命令reboot在重启设备的时候串口一直输入q，enter输入大写X，密码ys23#2ls29#4 串口输出please input password:
+=&gt; 
+=&gt;为进入救灾成功然标记，然后输入：setenv ipaddr 192.168.40.111
+setenv serverip 192.168.40.11
+setenv imagename 32.3.0.7.ext2
+run updata-image</t>
+  </si>
+  <si>
+    <t>2，登录成功后需要先判断//*[@id="qwert_firmware_ver"]里面的内容是否是E:\GIT\ROUTER_TEST\docs\upload\new里面文件名.bin之前的版本号一致，如果检测一致则证明路由器已经是新版本了，需要先升级到旧版本</t>
+  </si>
+  <si>
+    <t>ifconfig Bridge0 192.168.50.18</t>
+  </si>
+  <si>
+    <t>&gt; 多设备反复升级稳定性测试 昨天实现了这个用例，现在需要修改一下：1，你需要占用windows上面的两个串口分别是com7和com8 波特率都是115200 数据位都是8 奇偶校验都是none 停止位1，然后要先分别登录两台设备的串口，登录串口的账号密码是：root
+  R0uT3&amp;U&amp;s@l1nk46#3登录成功的标记是串口输出root@ROUTER:~#然后输入命令reboot然后设备会立马重启你要一致串口输入q+回车出现Enter : 后输入大写X回车出现打印please input password:输入密码ys23#2ls29#4出现=&gt;代表进入boot模式成功，然后在串口7里面输入setenv
+  ipaddr 172.168.0.10
+  setenv serverip 172.168.0.100
+  setenv imagename 32.3.0.7.ext2
+  run updata-image然后如果打印中有Loading: #####证明正在上传升级文件，然后等待打印written: OK证明烧录完成，等串口打印回到=&gt;时输入reset,如果打印resetting ...证明成功，等设备重启（大约等待30s）然后重新登录串口的账号密码是：root
+    R0uT3&amp;U&amp;s@l1nk46#3登录成功的标记是串口输出root@ROUTER:~# 输入命令ifconfig Bridge0 192.168.50.18 然后上面同步操作com8其中不同之处setenv ipaddr 172.168.0.11  ifconfig Bridge0 192.168.50.17 其他均一致，逻辑和判断均一致
+  2，这两台设备的登录账号密码默认为 admin password 3,登录成功后首选判断是否有修改密码的弹窗点击弹窗的Cancel按钮，4，检查登录首页的//*[@id="qwert_firmware_ver"]里面的版本号是否为：32.3.0.7 如果是则打印：烧录旧版本32.3.0.7成功，接下来进行新版本升级
+  5，跳转到升级页面#maintenance/upgrade/upgrade并刷新，点击上传文件按钮，上传文件路径是E:\GIT\ROUTER_TEST\docs\upload\new下面的文件，上传成功后开始升级，等待升级完成后登录页面继续判断版本是否为32.3.0.9如果成功则证明第一次升级成功，然后串口烧录旧版本，
+  页面升级新版本循环1000次 ；特别说明，参照现在这个升级用例的实现其中上传升级文件的方法要参照，另外就是需要独立控制两台设备进行独立操作</t>
+  </si>
+  <si>
     <t>漫游无ac场景测试.企业环境.1]金帆大厦600平部署8面板AP</t>
   </si>
   <si>
@@ -365,12 +679,6 @@
   </si>
   <si>
     <t>漫游无ac场景测试.企业环境.3]金帆大厦600平部署1吸顶ap+7面板面板AP</t>
-  </si>
-  <si>
-    <t>测试用例名称</t>
-  </si>
-  <si>
-    <t>备注</t>
   </si>
 </sst>
 </file>
@@ -1009,7 +1317,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1026,6 +1334,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1592,17 +1903,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P29"/>
+  <dimension ref="A1:P46"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="6.55555555555556" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="4" max="4" width="8" customWidth="1"/>
     <col min="5" max="5" width="35" customWidth="1"/>
     <col min="6" max="6" width="28.8888888888889" customWidth="1"/>
-    <col min="7" max="7" width="63.1111111111111" customWidth="1"/>
-    <col min="8" max="8" width="30" customWidth="1"/>
+    <col min="7" max="7" width="113.555555555556" customWidth="1"/>
+    <col min="8" max="8" width="40.5555555555556" customWidth="1"/>
     <col min="9" max="11" width="5" customWidth="1"/>
     <col min="12" max="13" width="15" customWidth="1"/>
     <col min="14" max="16" width="10" customWidth="1"/>
@@ -1658,7 +1969,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" ht="264" spans="1:16">
+    <row r="2" ht="168" spans="1:16">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1695,7 +2006,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" ht="120" spans="1:16">
+    <row r="4" ht="72" spans="1:16">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1738,7 +2049,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" ht="168" spans="1:16">
+    <row r="6" ht="108" spans="1:16">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1752,7 +2063,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" ht="132" spans="1:16">
+    <row r="7" ht="96" spans="1:16">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1769,7 +2080,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" ht="84" spans="1:16">
+    <row r="8" ht="60" spans="1:16">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1786,7 +2097,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" ht="216" spans="1:16">
+    <row r="9" ht="168" spans="1:16">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1806,7 +2117,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" ht="144" spans="1:16">
+    <row r="10" ht="108" spans="1:16">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1831,22 +2142,52 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" ht="120" spans="1:16">
       <c r="A12">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:16">
+      <c r="B12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" t="s">
+        <v>52</v>
+      </c>
+      <c r="G12" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" ht="24" spans="1:16">
       <c r="A13">
         <v>12</v>
       </c>
-    </row>
-    <row r="14" spans="1:16">
+      <c r="B13" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" t="s">
+        <v>54</v>
+      </c>
+      <c r="G13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" ht="36" spans="1:16">
       <c r="A14">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" ht="409.5" spans="1:16">
+      <c r="B14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" t="s">
+        <v>56</v>
+      </c>
+      <c r="G14" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="15" ht="36" spans="1:16">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1854,101 +2195,270 @@
         <v>50</v>
       </c>
       <c r="E15" t="s">
-        <v>51</v>
-      </c>
-      <c r="F15" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="G15" t="s">
-        <v>53</v>
-      </c>
-      <c r="H15" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="16" ht="108" spans="1:16">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" ht="36" spans="1:16">
       <c r="A16">
         <v>15</v>
       </c>
-      <c r="F16" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
+      <c r="B16" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" t="s">
+        <v>60</v>
+      </c>
+      <c r="G16" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17" ht="36" spans="1:8">
       <c r="A17">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:1">
+      <c r="B17" t="s">
+        <v>50</v>
+      </c>
+      <c r="E17" t="s">
+        <v>62</v>
+      </c>
+      <c r="G17" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18" ht="60" spans="1:8">
       <c r="A18">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="1:1">
+      <c r="B18" t="s">
+        <v>50</v>
+      </c>
+      <c r="E18" t="s">
+        <v>64</v>
+      </c>
+      <c r="G18" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" ht="36" spans="1:8">
       <c r="A19">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:1">
+      <c r="B19" t="s">
+        <v>50</v>
+      </c>
+      <c r="E19" t="s">
+        <v>66</v>
+      </c>
+      <c r="G19" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20" ht="120" spans="1:8">
       <c r="A20">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="1:1">
+      <c r="B20" t="s">
+        <v>50</v>
+      </c>
+      <c r="E20" t="s">
+        <v>68</v>
+      </c>
+      <c r="G20" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="21" ht="24" spans="1:8">
       <c r="A21">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" spans="1:1">
+      <c r="B21" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" ht="24" spans="1:8">
       <c r="A22">
         <v>21</v>
       </c>
-    </row>
-    <row r="23" spans="1:1">
+      <c r="B22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" ht="24" spans="1:8">
       <c r="A23">
         <v>22</v>
       </c>
-    </row>
-    <row r="24" spans="1:1">
+      <c r="B23" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" ht="24" spans="1:8">
       <c r="A24">
         <v>23</v>
       </c>
-    </row>
-    <row r="25" spans="1:1">
+      <c r="B24" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" ht="396" spans="1:8">
       <c r="A25">
+        <v>14</v>
+      </c>
+      <c r="B25" t="s">
+        <v>70</v>
+      </c>
+      <c r="E25" t="s">
+        <v>71</v>
+      </c>
+      <c r="F25" t="s">
+        <v>72</v>
+      </c>
+      <c r="G25" t="s">
+        <v>73</v>
+      </c>
+      <c r="H25" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26" ht="409.5" spans="1:8">
+      <c r="A26">
+        <v>15</v>
+      </c>
+      <c r="B26" t="s">
+        <v>70</v>
+      </c>
+      <c r="E26" t="s">
+        <v>75</v>
+      </c>
+      <c r="F26" t="s">
+        <v>72</v>
+      </c>
+      <c r="G26" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="27" ht="409.5" spans="1:8">
+      <c r="A27">
+        <v>16</v>
+      </c>
+      <c r="B27" t="s">
+        <v>70</v>
+      </c>
+      <c r="E27" t="s">
+        <v>77</v>
+      </c>
+      <c r="F27" t="s">
+        <v>72</v>
+      </c>
+      <c r="G27" t="s">
+        <v>78</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" ht="132" spans="1:8">
+      <c r="A32">
+        <v>21</v>
+      </c>
+      <c r="B32" t="s">
+        <v>80</v>
+      </c>
+      <c r="E32" t="s">
+        <v>81</v>
+      </c>
+      <c r="G32" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
-      <c r="A26">
+    <row r="36" spans="1:7">
+      <c r="A36">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
-      <c r="A27">
+    <row r="37" spans="1:7">
+      <c r="A37">
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
-      <c r="A28">
+    <row r="38" spans="1:7">
+      <c r="A38">
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
-      <c r="A29">
+    <row r="39" spans="1:7">
+      <c r="A39">
         <v>28</v>
+      </c>
+    </row>
+    <row r="40" ht="84" spans="1:7">
+      <c r="G40" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="42" ht="24" spans="1:7">
+      <c r="G42" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="G44" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="46" ht="240" spans="1:7">
+      <c r="G46" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" insertColumns="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:K162" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:K172" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <dataValidations count="2">
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="输入的值有误" error="您输入的值不在下拉框列表内." promptTitle="优先级" sqref="J2:J161" errorStyle="information">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="输入的值有误" error="您输入的值不在下拉框列表内." promptTitle="优先级" sqref="J2:J14 J15:J24 J25:J171" errorStyle="information">
       <formula1>"顶,高,中,低"</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="输入的值有误" error="您输入的值不在下拉框列表内." promptTitle="优先级" sqref="K2:K161" errorStyle="information">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="输入的值有误" error="您输入的值不在下拉框列表内." promptTitle="优先级" sqref="K2:K14 K15:K24 K25:K171" errorStyle="information">
       <formula1>"自动,手动"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1978,22 +2488,22 @@
     </row>
     <row r="2" ht="409" customHeight="1" spans="1:1">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" ht="409" customHeight="1" spans="1:1">
       <c r="A3" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" ht="409" customHeight="1" spans="1:1">
       <c r="A4" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" ht="409" customHeight="1" spans="1:1">
       <c r="A5" t="s">
-        <v>57</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" ht="409" customHeight="1"/>
@@ -2024,21 +2534,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>59</v>
-      </c>
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/用例步骤.xlsx
+++ b/用例步骤.xlsx
@@ -13,7 +13,7 @@
     <sheet name="页面元素" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">testcase!$A$1:$K$172</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">testcase!$A$1:$K$179</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="104">
   <si>
     <t>ID</t>
   </si>
@@ -230,6 +230,43 @@
 写线圈 .write_coil(address, value, unit=1)
 写寄存器 .write_register(address, value, unit=1)
 3&gt;进程B 要自己在本地模拟另一个Modbus Poll同样去与进程A进行交互，总体实现参照D:\WK\Milesight\AUTO\设备python3.9模块脚本\测试脚本\test_modbus.py</t>
+  </si>
+  <si>
+    <t>新Urapi库在新SDK上面的适配测试</t>
+  </si>
+  <si>
+    <t>1，参照用例“python3.9第三方库pymodbus验证”的实现方法
+2，登上设备后，查看路由器的ftp服务器是否开启，python3.9环境是否安装
+3，将脚本D:\WK\Milesight\项目\2025H2\维护\3x.3.0.1141.0.0.6迭代\U2\URDBAPI_test.py参照用例“python3.9第三方库pymodbus验证”里面上传的方式，上传后执行脚本，查看结果为Using db file: /tmp/urdbapi_test.db
+rmDBFile (cleanup) -&gt; None
+addValue(alpha, foo) -&gt; None
+addValue(alpha, {'n': 1}) -&gt; None
+addValue(beta, 123) -&gt; None
+showValue(alpha) -&gt; None
+showValue(beta) -&gt; None
+getList() -&gt; None
+updateValue(alpha, 'updated') -&gt; None
+showValue(alpha) -&gt; None
+delValue(beta) -&gt; None
+getList() -&gt; None
+rmDBFile (final cleanup) -&gt; None
+4，参照步骤3上传脚本D:\WK\Milesight\项目\2025H2\维护\3x.3.0.1141.0.0.6迭代\U2\URInterface_test.py参照用例“python3.9第三方库pymodbus验证”里面上传的方式，上传后执行脚本，查看结果为down(FE0) -&gt; True
+up(FE0) -&gt; True
+set_ipv4(FE0, 192.0.2.10, 255.255.255.0) -&gt; True
+set_mtu(FE0, 1500) -&gt; True
+set_mac(FE0, 00:11:22:33:44:55) -&gt; True
+add_static_route(FE0, 198.51.100.0/24) -&gt; True
+add_default_route(FE0, 192.0.2.1) -&gt; True
+del_static_route(FE0, 198.51.100.0/24) -&gt; True
+del_default_route(FE0, 192.0.2.1) -&gt; True
+send_at_cmd(ATI) -&gt; 2025-12-12 08:14:00: [SEQ0,ID0]&lt;&lt;&lt; OK
+5,参照步骤3上传脚本D:\WK\Milesight\项目\2025H2\维护\3x.3.0.1141.0.0.6迭代\U2\URRouterInfo_test.py参照用例“python3.9第三方库pymodbus验证”里面上传的方式，上传后执行脚本，查看结果为get_eth_portList -&gt; [{'port': 'WAN', 'status': 1, 'connect_state': 1, 'cur_speed': '100Mbps', 'cur_duplex': 'full'}, {'port': 'LAN1', 'status': 1, 'connect_state': 0, 'cur_speed': '-', 'cur_duplex': '-'}, {'port': 'LAN2', 'status': 1, 'connect_state': 0, 'cur_speed': '-', 'cur_duplex': '-'}, {'port': 'LAN3', 'status': 1, 'connect_state': 1, 'cur_speed': '100Mbps', 'cur_duplex': 'full'}, {'port': 'LAN4', 'status': 1, 'connect_state': 0, 'cur_speed': '-', 'cur_duplex': '-'}]
+get_firmware_info -&gt; {'model': 'UR35-L04AU-G', 'sn': '6219E2756052', 'firmware_ver': '35.3.0.11-a1', 'hardware_ver': 'V2.0', 'uptime': 7574, 'local_time': '2025-12-12 08:16:06 Friday', 'cpu_load': '8%', 'memory_free': 49, 'memory_total': 128, 'flash_free': 81, 'flash_total': 128}
+get_cellular_status -&gt; {'model': {'modem_status': 'Ready', 'model': 'EC20F', 'version': 'EC20CEHCLGR08A02M1G', 'cur_sim': 'SIM1', 'signal': '31asu (-51dBm)', 'band': '4G(B1)', 'rsrp': '-78dbm', 'rsrq': '-6db', 'sinr': '26db', 'register': 'Registered (Home network)', 'imsi': '460115211257157', 'iccid': '89860324245920231421', 'net_provider': 'CHN-CT', 'net_type': 'FDD LTE', 'plmnid': '46011', 'lac': '5f0c', 'cellid': 'e0b70b', 'imei': '869128065899956'}, 'apn1': {'status': 'Connected', 'ip': '10.72.16.102', 'netmask': '255.255.255.252', 'gate': '10.72.16.101', 'dns': '218.85.152.99', 'sec_dns': '218.85.157.99', 'dnsv6': '240e:14:e000:0:0:0:0:1', 'sec_dnsv6': '240e:14:6000:0:0:0:0:1', 'ipv6': '240e:464:2010:934b:6c5f:4323:4578:60ee/64', 'gatev6': '240e:464:2010:934b:d454:15ab:e362:8b8', 'time': '0 days, 02:04:13'}, 'apn2': {'status': 'Disabled', 'ip': '0.0.0.0', 'netmask': '0.0.0.0', 'gate': '0.0.0.0', 'dns': '0.0.0.0', 'sec_dns': '0.0.0.0', 'dnsv6': '::', 'sec_dnsv6': '::', 'ipv6': '::', 'gatev6': '::', 'time': '0 days, 00:00:00'}, 'apn3': {'status': 'Disabled', 'ip': '0.0.0.0', 'netmask': '0.0.0.0', 'gate': '0.0.0.0', 'dns': '0.0.0.0', 'sec_dns': '0.0.0.0', 'dnsv6': '::', 'sec_dnsv6': '::', 'ipv6': '::', 'gatev6': '::', 'time': '0 days, 00:00:00'}}
+get_wan_status -&gt; {'grey': 0, 'enable_wan': 1, 'port': 'WAN', 'protocol': 0, 'mtu': 1500, 'enable_nat': 1, 'pri_dns': '223.5.5.5', 'sec_dns': '114.114.114.114', 'pri_dns6': '', 'sec_dns6': '', 'static': {'ip_address': '', 'netmask': '255.255.255.0', 'gateway': '192.168.50.1', 'ip6addr': '', 'ip6prefixlen': 64, 'ip6gw': '', 'multi_ip': [{'id': 'z7gQ40xlkX9w62x4z6b51f3Wp34pWE6I1Q5Jd3o9SJ49k833gXsew7j5EO0C', 'ip_addr': '192.0.2.10', 'mask': '255.255.255.0'}]}, 'dhcp': {'mtu': 1500, 'use_peer_dns': 0}, 'pppoe': {'mtu': 1500, 'use_peer_dns': 0}, 'pppoev6': {'mtu': 1500, 'use_peer_dns': 0}}
+get_bridge_status -&gt; {'stp': 0, 'name': 'Bridge0', 'mtu': 1500, 'ip_address': '192.168.3.1', 'netmask': '255.255.255.0', 'ipv6_address': '', 'multi_ip': [], 'deletable': [1], 'members': ['vlan 1'], 'list': [], 'ip_passthrough_enable': False}
+get_serial_info -&gt; '{"serial1": "RS232", "serial2": "RS485"}'
+get_di_status -&gt; {'di': 1}</t>
   </si>
   <si>
     <r>
@@ -381,17 +418,47 @@
     <t>参照D:\WK\Milesight\AUTO\port_check.py里面的def configure_vpn_server_ports(driver, wait, ports, vpn_config):所不同的是这次输入的端口号不一样需要和用例“端口冲突检测测试（全端口扫描）”里面保持一直 另外就是这些端口都必须弹窗提醒端口冲突，如果不弹在证明用例失败</t>
   </si>
   <si>
-    <t>自定义端口两两冲突检测</t>
+    <t xml:space="preserve">openvpenserver与防火墙自定义端口冲突检测
+</t>
   </si>
   <si>
     <t>1，去防火墙界面配置ftp端口为1111（配置方法参照用例：设备防火墙界面检查静态端口冲突）这里要区别是只配置ftp端口配置完后要先启用ftp勾选然后保存并点击应用
-2，去openvpn界面配置端口为1111（配置方法参照用例：设备open vpn界面端口冲突）这里需要弹窗提醒才算通过
-3，去端口映射界面配置端口为1111（配置方法参照用例：端口冲突检测测试（全端口扫描）里面配置端口映射部分）这里需要弹窗提醒才算通过
-4，去设备串口1界面端口配置端口为1111（配置方法参照用例：设备去串口1界面端口冲突）这里需要弹窗提醒才算通过
-5，去设备串口2界面端口配置端口为1111（配置方法参照用例：设备去串口2界面端口冲突）这里需要弹窗提醒才算通过
-6，去设备modbus TCP界面端口配置端口为1111（配置方法参照用例：设备去modbus TCP界面端口冲突）这里需要弹窗提醒才算通过
-7，去SNMP 页面配置端口为1111（配置方法参照用例：设备去SNMP界面端口冲突）这里需要弹窗提醒才算通过
-8，去GPS 页面配置端口为1111（配置方法参照用例：设备去GPS界面端口冲突）这里需要弹窗提醒才算通过</t>
+2，去openvpn界面配置端口为1111（配置方法参照用例：设备open vpn界面端口冲突，这个openvpn需要配置其他参数全部也参照这条用例）这里需要弹窗提醒才算通过</t>
+  </si>
+  <si>
+    <t>端口映射与防火墙自定义端口冲突检测</t>
+  </si>
+  <si>
+    <t>1，去防火墙界面配置ftp端口为1111（配置方法参照用例：设备防火墙界面检查静态端口冲突）这里要区别是只配置ftp端口配置完后要先启用ftp勾选然后保存并点击应用
+2，去端口映射界面配置端口为1111（配置方法参照用例：端口冲突检测测试（全端口扫描）里面配置端口映射部分，这个功能其他配置部分也按照这个用例里面的去补充）这里需要弹窗提醒才算通过</t>
+  </si>
+  <si>
+    <t>串口1和串口2界面与防火墙自定义端口冲突检测</t>
+  </si>
+  <si>
+    <t>1，去防火墙界面配置ftp端口为1111（配置方法参照用例：设备防火墙界面检查静态端口冲突）这里要区别是只配置ftp端口配置完后要先启用ftp勾选然后保存并点击应用4，去设备串口1界面端口配置端口为1111（配置方法参照用例：设备去串口1界面端口冲突）这里需要弹窗提醒才算通过
+2，去设备串口2界面端口配置端口为1111（配置方法参照用例：设备去串口2界面端口冲突）这里需要弹窗提醒才算通过</t>
+  </si>
+  <si>
+    <t>modbus TCP与防火墙自定义端口冲突检测</t>
+  </si>
+  <si>
+    <t>1，去防火墙界面配置ftp端口为1111（配置方法参照用例：设备防火墙界面检查静态端口冲突）这里要区别是只配置ftp端口配置完后要先启用ftp勾选然后保存并点击应用4，去设备串口1界面端口配置端口为1111（配置方法参照用例：设备去串口1界面端口冲突）这里需要弹窗提醒才算通过
+2，去设备modbus TCP界面端口配置端口为1111（配置方法参照用例：设备去modbus TCP界面端口冲突）这里需要弹窗提醒才算通过</t>
+  </si>
+  <si>
+    <t>SNMP与防火墙自定义端口冲突检测</t>
+  </si>
+  <si>
+    <t>1，去防火墙界面配置ftp端口为1111（配置方法参照用例：设备防火墙界面检查静态端口冲突）这里要区别是只配置ftp端口配置完后要先启用ftp勾选然后保存并点击应用4，去设备串口1界面端口配置端口为1111（配置方法参照用例：设备去串口1界面端口冲突）这里需要弹窗提醒才算通过
+2，去SNMP 页面配置端口为1111（配置方法参照用例：设备去SNMP界面端口冲突）这里需要弹窗提醒才算通过</t>
+  </si>
+  <si>
+    <t>GPS与防火墙自定义端口冲突检测</t>
+  </si>
+  <si>
+    <t>1，去防火墙界面配置ftp端口为1111（配置方法参照用例：设备防火墙界面检查静态端口冲突）这里要区别是只配置ftp端口配置完后要先启用ftp勾选然后保存并点击应用4，去设备串口1界面端口配置端口为1111（配置方法参照用例：设备去串口1界面端口冲突）这里需要弹窗提醒才算通过
+2，去GPS 页面配置端口为1111（配置方法参照用例：设备去GPS界面端口冲突）这里需要弹窗提醒才算通过</t>
   </si>
   <si>
     <t>功能用例/服务/MQTT</t>
@@ -634,7 +701,7 @@
     <t>稳定性</t>
   </si>
   <si>
-    <t>多设备反复升级稳定性测试</t>
+    <t>多设备固定两版本反复升级稳定性测试</t>
   </si>
   <si>
     <t>1，我有两台，固定ip 192.168.50.17  用户admin 密码admin1   固定ip：192.168.50.18 用户admin 密码admin1 需要对这两台设备进行循环升级新旧版本，新版本路径：E:\GIT\ROUTER_TEST\docs\upload\new 旧版本路径：E:\GIT\ROUTER_TEST\docs\upload\old
@@ -646,30 +713,24 @@
 8，两台设备独立进行并行测试</t>
   </si>
   <si>
-    <t>（特别说明50.17这个设备对应的串口是com8  50.18这个设备对应的是com7）登录串口然后输入命令reboot在重启设备的时候串口一直输入q，enter输入大写X，密码ys23#2ls29#4 串口输出please input password:
-=&gt; 
-=&gt;为进入救灾成功然标记，然后输入：setenv ipaddr 192.168.40.111
-setenv serverip 192.168.40.11
-setenv imagename 32.3.0.7.ext2
-run updata-image</t>
-  </si>
-  <si>
-    <t>2，登录成功后需要先判断//*[@id="qwert_firmware_ver"]里面的内容是否是E:\GIT\ROUTER_TEST\docs\upload\new里面文件名.bin之前的版本号一致，如果检测一致则证明路由器已经是新版本了，需要先升级到旧版本</t>
-  </si>
-  <si>
-    <t>ifconfig Bridge0 192.168.50.18</t>
-  </si>
-  <si>
-    <t>&gt; 多设备反复升级稳定性测试 昨天实现了这个用例，现在需要修改一下：1，你需要占用windows上面的两个串口分别是com7和com8 波特率都是115200 数据位都是8 奇偶校验都是none 停止位1，然后要先分别登录两台设备的串口，登录串口的账号密码是：root
-  R0uT3&amp;U&amp;s@l1nk46#3登录成功的标记是串口输出root@ROUTER:~#然后输入命令reboot然后设备会立马重启你要一致串口输入q+回车出现Enter : 后输入大写X回车出现打印please input password:输入密码ys23#2ls29#4出现=&gt;代表进入boot模式成功，然后在串口7里面输入setenv
-  ipaddr 172.168.0.10
-  setenv serverip 172.168.0.100
-  setenv imagename 32.3.0.7.ext2
-  run updata-image然后如果打印中有Loading: #####证明正在上传升级文件，然后等待打印written: OK证明烧录完成，等串口打印回到=&gt;时输入reset,如果打印resetting ...证明成功，等设备重启（大约等待30s）然后重新登录串口的账号密码是：root
-    R0uT3&amp;U&amp;s@l1nk46#3登录成功的标记是串口输出root@ROUTER:~# 输入命令ifconfig Bridge0 192.168.50.18 然后上面同步操作com8其中不同之处setenv ipaddr 172.168.0.11  ifconfig Bridge0 192.168.50.17 其他均一致，逻辑和判断均一致
-  2，这两台设备的登录账号密码默认为 admin password 3,登录成功后首选判断是否有修改密码的弹窗点击弹窗的Cancel按钮，4，检查登录首页的//*[@id="qwert_firmware_ver"]里面的版本号是否为：32.3.0.7 如果是则打印：烧录旧版本32.3.0.7成功，接下来进行新版本升级
-  5，跳转到升级页面#maintenance/upgrade/upgrade并刷新，点击上传文件按钮，上传文件路径是E:\GIT\ROUTER_TEST\docs\upload\new下面的文件，上传成功后开始升级，等待升级完成后登录页面继续判断版本是否为32.3.0.9如果成功则证明第一次升级成功，然后串口烧录旧版本，
-  页面升级新版本循环1000次 ；特别说明，参照现在这个升级用例的实现其中上传升级文件的方法要参照，另外就是需要独立控制两台设备进行独立操作</t>
+    <t>遍历历史所有版本升级到最新稳定性测试</t>
+  </si>
+  <si>
+    <t>这里更用例“多设备固定在两个版本之间反复升级稳定性测试（串口烧录 + Web升级）”的逻辑一样，只是不是循环1000次，而是要遍历E:\GIT\ROUTER_TEST\docs\upload\old_all里面所有的文件，每次烧录旧版本旧遍历一个版本直到所有旧版本遍历完成，新版本的路径还是不变，依旧是通过web去升级，和用例“多设备固定在两个版本之间反复升级稳定性测试（串口烧录 + Web升级）”一致</t>
+  </si>
+  <si>
+    <t>满配置稳定性挂测</t>
+  </si>
+  <si>
+    <t>1，</t>
+  </si>
+  <si>
+    <t>web固定两版本循环升级稳定性验证</t>
+  </si>
+  <si>
+    <t>1，登陆到路由器，跳转到升级页面（设备默认使用的是https登陆，会响应比较慢需要增长一点响应时间）参照用例“多设备固定两版本反复升级稳定性测试”里面web升级版本的部分
+2，上传升级文件，点击升级
+3，等待上传文件完成，同时判断页面的&lt;span class="ys-upload-error"&gt;Importing firmware. Please stay on this page till upgrade is finished.&lt;/span&gt;里面有没有打印Failed to upload. Please try again 如果有则记录次数证明上传文件失败，如果没有则证明上传成功基线点击升级并进入下一轮循环，循环100次</t>
   </si>
   <si>
     <t>漫游无ac场景测试.企业环境.1]金帆大厦600平部署8面板AP</t>
@@ -1903,7 +1964,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P46"/>
+  <dimension ref="A1:P80"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1990,7 +2051,7 @@
       <c r="L2" s="3"/>
     </row>
     <row r="3" ht="24" spans="1:16">
-      <c r="A3">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" t="s">
@@ -2007,7 +2068,7 @@
       </c>
     </row>
     <row r="4" ht="72" spans="1:16">
-      <c r="A4">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" t="s">
@@ -2027,7 +2088,7 @@
       </c>
     </row>
     <row r="5" ht="409.5" spans="1:16">
-      <c r="A5">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" t="s">
@@ -2050,7 +2111,7 @@
       </c>
     </row>
     <row r="6" ht="108" spans="1:16">
-      <c r="A6">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" t="s">
@@ -2064,7 +2125,7 @@
       </c>
     </row>
     <row r="7" ht="96" spans="1:16">
-      <c r="A7">
+      <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" t="s">
@@ -2081,7 +2142,7 @@
       </c>
     </row>
     <row r="8" ht="60" spans="1:16">
-      <c r="A8">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" t="s">
@@ -2098,7 +2159,7 @@
       </c>
     </row>
     <row r="9" ht="168" spans="1:16">
-      <c r="A9">
+      <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" t="s">
@@ -2117,348 +2178,606 @@
         <v>32</v>
       </c>
     </row>
-    <row r="10" ht="108" spans="1:16">
-      <c r="A10">
+    <row r="10" ht="409.5" spans="1:16">
+      <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" t="s">
         <v>45</v>
       </c>
-      <c r="E10" t="s">
+      <c r="G10" t="s">
         <v>46</v>
       </c>
-      <c r="F10" t="s">
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5"/>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5"/>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5"/>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="5"/>
+    </row>
+    <row r="15" ht="108" spans="1:16">
+      <c r="A15" s="2">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="G10" t="s">
+      <c r="E15" t="s">
         <v>48</v>
       </c>
-      <c r="H10" t="s">
+      <c r="F15" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="11" spans="1:16">
-      <c r="A11">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" ht="120" spans="1:16">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="G15" t="s">
         <v>50</v>
       </c>
-      <c r="E12" t="s">
+      <c r="H15" t="s">
         <v>51</v>
       </c>
-      <c r="F12" t="s">
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" ht="120" spans="1:8">
+      <c r="A17" s="2">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
         <v>52</v>
       </c>
-      <c r="G12" t="s">
+      <c r="E17" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="13" ht="24" spans="1:16">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="F17" t="s">
+        <v>54</v>
+      </c>
+      <c r="G17" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="18" ht="24" spans="1:8">
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" t="s">
+        <v>56</v>
+      </c>
+      <c r="G18" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="19" ht="36" spans="1:8">
+      <c r="A19" s="2">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>52</v>
+      </c>
+      <c r="E19" t="s">
+        <v>58</v>
+      </c>
+      <c r="G19" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="20" ht="36" spans="1:8">
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>52</v>
+      </c>
+      <c r="E20" t="s">
+        <v>60</v>
+      </c>
+      <c r="G20" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="21" ht="36" spans="1:8">
+      <c r="A21" s="2">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>52</v>
+      </c>
+      <c r="E21" t="s">
+        <v>62</v>
+      </c>
+      <c r="G21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" ht="36" spans="1:8">
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>52</v>
+      </c>
+      <c r="E22" t="s">
+        <v>64</v>
+      </c>
+      <c r="G22" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" ht="60" spans="1:8">
+      <c r="A23" s="2">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>52</v>
+      </c>
+      <c r="E23" t="s">
+        <v>66</v>
+      </c>
+      <c r="G23" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="24" ht="36" spans="1:8">
+      <c r="A24" s="2">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>52</v>
+      </c>
+      <c r="E24" t="s">
+        <v>68</v>
+      </c>
+      <c r="G24" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="25" ht="48" spans="1:8">
+      <c r="A25" s="2">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>52</v>
+      </c>
+      <c r="E25" t="s">
+        <v>70</v>
+      </c>
+      <c r="G25" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="26" ht="48" spans="1:8">
+      <c r="A26" s="2">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>52</v>
+      </c>
+      <c r="E26" t="s">
+        <v>72</v>
+      </c>
+      <c r="G26" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="27" ht="48" spans="1:8">
+      <c r="A27" s="2">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>52</v>
+      </c>
+      <c r="E27" t="s">
+        <v>74</v>
+      </c>
+      <c r="G27" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="28" ht="48" spans="1:8">
+      <c r="A28" s="2">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>52</v>
+      </c>
+      <c r="E28" t="s">
+        <v>76</v>
+      </c>
+      <c r="G28" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="29" ht="48" spans="1:8">
+      <c r="A29" s="2">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>52</v>
+      </c>
+      <c r="E29" t="s">
+        <v>78</v>
+      </c>
+      <c r="G29" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="30" ht="48" spans="1:8">
+      <c r="A30" s="2">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>52</v>
+      </c>
+      <c r="E30" t="s">
+        <v>80</v>
+      </c>
+      <c r="G30" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" ht="396" spans="1:8">
+      <c r="A32" s="2">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>82</v>
+      </c>
+      <c r="E32" t="s">
+        <v>83</v>
+      </c>
+      <c r="F32" t="s">
+        <v>84</v>
+      </c>
+      <c r="G32" t="s">
+        <v>85</v>
+      </c>
+      <c r="H32" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="33" ht="409.5" spans="1:8">
+      <c r="A33" s="2">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>82</v>
+      </c>
+      <c r="E33" t="s">
+        <v>87</v>
+      </c>
+      <c r="F33" t="s">
+        <v>84</v>
+      </c>
+      <c r="G33" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="34" ht="409.5" spans="1:8">
+      <c r="A34" s="2">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>82</v>
+      </c>
+      <c r="E34" t="s">
+        <v>89</v>
+      </c>
+      <c r="F34" t="s">
+        <v>84</v>
+      </c>
+      <c r="G34" t="s">
+        <v>90</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" ht="132" spans="1:8">
+      <c r="A39" s="2">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>92</v>
+      </c>
+      <c r="E39" t="s">
+        <v>93</v>
+      </c>
+      <c r="G39" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="40" ht="36" spans="1:8">
+      <c r="A40" s="2">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>92</v>
+      </c>
+      <c r="E40" t="s">
+        <v>95</v>
+      </c>
+      <c r="G40" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="2">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>92</v>
+      </c>
+      <c r="E41" t="s">
+        <v>97</v>
+      </c>
+      <c r="G41" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="42" ht="72" spans="1:8">
+      <c r="A42" s="2">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>92</v>
+      </c>
+      <c r="E42" t="s">
+        <v>99</v>
+      </c>
+      <c r="G42" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" s="2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" s="2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" s="2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" s="2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" s="2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" s="2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="2">
         <v>50</v>
       </c>
-      <c r="E13" t="s">
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" s="2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="2">
         <v>54</v>
       </c>
-      <c r="G13" t="s">
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="2">
         <v>55</v>
       </c>
     </row>
-    <row r="14" ht="36" spans="1:16">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>50</v>
-      </c>
-      <c r="E14" t="s">
+    <row r="57" spans="1:1">
+      <c r="A57" s="2">
         <v>56</v>
       </c>
-      <c r="G14" t="s">
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="2">
         <v>57</v>
       </c>
     </row>
-    <row r="15" ht="36" spans="1:16">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E15" t="s">
+    <row r="59" spans="1:1">
+      <c r="A59" s="2">
         <v>58</v>
       </c>
-      <c r="G15" t="s">
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" s="2">
         <v>59</v>
       </c>
     </row>
-    <row r="16" ht="36" spans="1:16">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>50</v>
-      </c>
-      <c r="E16" t="s">
+    <row r="61" spans="1:1">
+      <c r="A61" s="2">
         <v>60</v>
       </c>
-      <c r="G16" t="s">
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="2">
         <v>61</v>
       </c>
     </row>
-    <row r="17" ht="36" spans="1:8">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17" t="s">
-        <v>50</v>
-      </c>
-      <c r="E17" t="s">
+    <row r="63" spans="1:1">
+      <c r="A63" s="2">
         <v>62</v>
       </c>
-      <c r="G17" t="s">
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="2">
         <v>63</v>
       </c>
     </row>
-    <row r="18" ht="60" spans="1:8">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18" t="s">
-        <v>50</v>
-      </c>
-      <c r="E18" t="s">
+    <row r="65" spans="1:1">
+      <c r="A65" s="2">
         <v>64</v>
       </c>
-      <c r="G18" t="s">
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="2">
         <v>65</v>
       </c>
     </row>
-    <row r="19" ht="36" spans="1:8">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19" t="s">
-        <v>50</v>
-      </c>
-      <c r="E19" t="s">
+    <row r="67" spans="1:1">
+      <c r="A67" s="2">
         <v>66</v>
       </c>
-      <c r="G19" t="s">
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="2">
         <v>67</v>
       </c>
     </row>
-    <row r="20" ht="120" spans="1:8">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20" t="s">
-        <v>50</v>
-      </c>
-      <c r="E20" t="s">
+    <row r="69" spans="1:1">
+      <c r="A69" s="2">
         <v>68</v>
       </c>
-      <c r="G20" t="s">
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" s="2">
         <v>69</v>
       </c>
     </row>
-    <row r="21" ht="24" spans="1:8">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22" ht="24" spans="1:8">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="23" ht="24" spans="1:8">
-      <c r="A23">
-        <v>22</v>
-      </c>
-      <c r="B23" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="24" ht="24" spans="1:8">
-      <c r="A24">
-        <v>23</v>
-      </c>
-      <c r="B24" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="25" ht="396" spans="1:8">
-      <c r="A25">
-        <v>14</v>
-      </c>
-      <c r="B25" t="s">
+    <row r="71" spans="1:1">
+      <c r="A71" s="2">
         <v>70</v>
       </c>
-      <c r="E25" t="s">
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" s="2">
         <v>71</v>
       </c>
-      <c r="F25" t="s">
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" s="2">
         <v>72</v>
       </c>
-      <c r="G25" t="s">
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" s="2">
         <v>73</v>
       </c>
-      <c r="H25" t="s">
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" s="2">
         <v>74</v>
       </c>
     </row>
-    <row r="26" ht="409.5" spans="1:8">
-      <c r="A26">
-        <v>15</v>
-      </c>
-      <c r="B26" t="s">
-        <v>70</v>
-      </c>
-      <c r="E26" t="s">
+    <row r="76" spans="1:1">
+      <c r="A76" s="2">
         <v>75</v>
       </c>
-      <c r="F26" t="s">
-        <v>72</v>
-      </c>
-      <c r="G26" t="s">
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" s="2">
         <v>76</v>
       </c>
     </row>
-    <row r="27" ht="409.5" spans="1:8">
-      <c r="A27">
-        <v>16</v>
-      </c>
-      <c r="B27" t="s">
-        <v>70</v>
-      </c>
-      <c r="E27" t="s">
+    <row r="78" spans="1:1">
+      <c r="A78" s="2">
         <v>77</v>
       </c>
-      <c r="F27" t="s">
-        <v>72</v>
-      </c>
-      <c r="G27" t="s">
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" s="2">
         <v>78</v>
       </c>
-      <c r="H27" s="6" t="s">
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" s="2">
         <v>79</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
-      <c r="A28">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
-      <c r="A29">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
-      <c r="A30">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
-      <c r="A31">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="32" ht="132" spans="1:8">
-      <c r="A32">
-        <v>21</v>
-      </c>
-      <c r="B32" t="s">
-        <v>80</v>
-      </c>
-      <c r="E32" t="s">
-        <v>81</v>
-      </c>
-      <c r="G32" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="40" ht="84" spans="1:7">
-      <c r="G40" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="42" ht="24" spans="1:7">
-      <c r="G42" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="G44" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="46" ht="240" spans="1:7">
-      <c r="G46" t="s">
-        <v>86</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" insertColumns="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:K172" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:K179" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <dataValidations count="2">
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="输入的值有误" error="您输入的值不在下拉框列表内." promptTitle="优先级" sqref="J2:J14 J15:J24 J25:J171" errorStyle="information">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="输入的值有误" error="您输入的值不在下拉框列表内." promptTitle="优先级" sqref="J2:J9 J10:J14 J15:J178" errorStyle="information">
       <formula1>"顶,高,中,低"</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="输入的值有误" error="您输入的值不在下拉框列表内." promptTitle="优先级" sqref="K2:K14 K15:K24 K25:K171" errorStyle="information">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" errorTitle="输入的值有误" error="您输入的值不在下拉框列表内." promptTitle="优先级" sqref="K2:K9 K10:K14 K15:K178" errorStyle="information">
       <formula1>"自动,手动"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2488,22 +2807,22 @@
     </row>
     <row r="2" ht="409" customHeight="1" spans="1:1">
       <c r="A2" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" ht="409" customHeight="1" spans="1:1">
       <c r="A3" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
     </row>
     <row r="4" ht="409" customHeight="1" spans="1:1">
       <c r="A4" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" ht="409" customHeight="1" spans="1:1">
       <c r="A5" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" ht="409" customHeight="1"/>
